--- a/benchmark/generated_files/RIC-1_M_016.xlsx
+++ b/benchmark/generated_files/RIC-1_M_016.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F160"/>
+  <dimension ref="A2:F160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -431,17 +431,10 @@
     <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Movimenti al 28/02/2026</t>
-        </is>
-      </c>
-    </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Intestatario: Sofia Rossi</t>
+          <t>Movimenti al 28/02/2026</t>
         </is>
       </c>
     </row>
@@ -452,45 +445,45 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Tipo conto: Carta ricaricabile</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Filiale: SEDE CENTRALE</t>
+        </is>
+      </c>
+    </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Codice cliente: 870023</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Divisa: EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Periodo: 01/01/2026 - 28/02/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Filiale: SEDE CENTRALE</t>
+          <t>Intestatario: Sofia Rossi</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Banca: PostePay Evolution</t>
+          <t>Codice cliente: 638648</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Tipo conto: Carta ricaricabile</t>
+          <t>Divisa: EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Banca: PostePay Evolution</t>
         </is>
       </c>
     </row>
@@ -531,15 +524,15 @@
         <v>46023</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46024</v>
+        <v>46025</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 5831 ESSELUNGA S.P.A.</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 7185 NATURA COLOGNO MONZESE</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>65.06999999999999</v>
+        <v>30.74</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -552,15 +545,15 @@
         <v>46023</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46024</v>
+        <v>46023</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Disposizione - RIF:210033191 BEN. TINTORIA RAPIDA CENTRO</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 5313 THUN FLAMINIO</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>88.47</v>
+        <v>30.09</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -570,18 +563,18 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B16" s="2" t="n">
         <v>46024</v>
       </c>
-      <c r="B16" s="2" t="n">
-        <v>46026</v>
-      </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AMAZON.IT MARKETPLACE - ORDINE 402-218929941</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>11.88</v>
+          <t>RICARICA POSTEPAY DA CONTO 0123456 ORD. SOFIA ROSSI</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>135.58</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -594,15 +587,15 @@
         <v>46024</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46024</v>
+        <v>46026</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 2874 TRATTORIA LA PERGOLA</t>
+          <t>Addebito SDD - ACI BOLLO AUTO TARGA PW411CR</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>27.95</v>
+        <v>35.59</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -615,15 +608,15 @@
         <v>46024</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46024</v>
+        <v>46026</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 17,67 EUR DEL 02.01.2026 A (ITA) STAZIONE Q8</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 7710 O'TACOS FIRENZE</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>17.67</v>
+        <v>47.5</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -640,11 +633,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 776,37 EUR DEL 02.01.2026 A (ITA) CARTOLIBRERIA IL PAPIRO</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 7715 MERCATÒ BIG</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>776.37</v>
+        <v>155.1</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -654,18 +647,18 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46025</v>
+        <v>46024</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46025</v>
+        <v>46024</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 528,66 EUR DEL 03.01.2026 A (ITA) LIBRERIA FELTRINELLI</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>528.66</v>
+          <t>RICARICA POSTEPAY DA CONTO 0123456 ORD. SOFIA ROSSI</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>73.94</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -682,11 +675,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 45,33 EUR DEL 03.01.2026 A (ITA) PIZZERIA NAPOLI</t>
+          <t>Pagam. POS - PAGAMENTO POS 35,23 EUR DEL 03.01.2026 A (ITA) BAR CENTRALE</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>45.33</v>
+        <v>35.23</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -696,18 +689,18 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
+        <v>46025</v>
+      </c>
+      <c r="B22" s="2" t="n">
         <v>46026</v>
       </c>
-      <c r="B22" s="2" t="n">
-        <v>46028</v>
-      </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 42,85 EUR DEL 04.01.2026 A (ITA) ESSELUNGA MILANO</t>
+          <t>Pagam. POS - PAGAMENTO POS 63,69 EUR DEL 03.01.2026 A (ITA) STAZIONE Q8</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>42.85</v>
+        <v>63.69</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -720,15 +713,15 @@
         <v>46026</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46026</v>
+        <v>46027</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Disposizione - RIF:210544147 BEN. TINTORIA RAPIDA CENTRO</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 3524 BLUESPIRIT</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.62</v>
+        <v>41.7</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -738,18 +731,18 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>46028</v>
+        <v>46026</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>46028</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 25,67 EUR DEL 06.01.2026 A (ITA) ROSTICCERIA DA MARIO</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 7814 MPREIS SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>25.67</v>
+        <v>28.51</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -759,18 +752,18 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>46028</v>
+        <v>46026</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46028</v>
+        <v>46027</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Disposizione - RIF:217134635 BEN. TINTORIA RAPIDA CENTRO</t>
+          <t>Addebito SDD - GOOGLE *CLOUD STORAGE</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>94.56999999999999</v>
+        <v>11.2</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -780,18 +773,18 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>46028</v>
+        <v>46027</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>46028</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 5080 OVS S.P.A.</t>
+          <t>Pagam. POS - PAGAMENTO POS 495,48 EUR DEL 05.01.2026 A (ITA) LIBRERIA FELTRINELLI</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>86.70999999999999</v>
+        <v>495.48</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -801,18 +794,18 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>46029</v>
+        <v>46027</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>46029</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 26,56 EUR DEL 07.01.2026 A (ITA) PESCHERIA DEL PORTO</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 4577 TRATTORIA LA PERGOLA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>26.56</v>
+        <v>30.81</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -822,18 +815,18 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>46029</v>
+        <v>46027</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46030</v>
+        <v>46027</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 26,28 EUR DEL 07.01.2026 A (ITA) CONAD CITY ROMA</t>
+          <t>Pagam. POS - PAGAMENTO POS 163,79 EUR DEL 05.01.2026 A (ITA) PANIFICIO TOSI</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>26.28</v>
+        <v>163.79</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -843,18 +836,18 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>46030</v>
+        <v>46028</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46032</v>
+        <v>46028</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 2362 TRATTORIA LA PERGOLA</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 6951 FRANCO MANCA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>47.39</v>
+        <v>40.89</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -864,18 +857,18 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>46030</v>
+        <v>46028</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46032</v>
+        <v>46029</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Addebito SDD - DELIVEROO ITALY SRL</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>40.61</v>
+          <t>RICARICA POSTEPAY DA CONTO 0123456 ORD. SOFIA ROSSI</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>238.16</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -885,18 +878,18 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Addebito SDD - NETFLIX INTERNATIONAL B.V.</t>
+          <t>Pagam. POS - PAGAMENTO POS 109,09 EUR DEL 07.01.2026 A (ITA) GULLIVER</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.41</v>
+        <v>109.09</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -906,18 +899,18 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>46030</v>
+        <v>46029</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46032</v>
+        <v>46029</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 11,89 EUR DEL 08.01.2026 A (ITA) LIDL ITALIA SRL</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 4677 INCOOP CAGLIARI</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.89</v>
+        <v>46.36</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -927,18 +920,18 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>46031</v>
+        <v>46029</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46033</v>
+        <v>46029</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Disposizione - RIF:217214397 BEN. OFFICINA MECCANICA BRAMBILLA</t>
+          <t>Addebito SDD - GENERALI ITALIA POLIZZA VITA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>43.15</v>
+        <v>12.89</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -948,18 +941,18 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>46031</v>
+        <v>46030</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46031</v>
+        <v>46030</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 81,21 EUR DEL 09.01.2026 A (ITA) H&amp;M HENNES AND MAURITZ</t>
+          <t>Pagam. POS - PAGAMENTO POS 482,70 EUR DEL 08.01.2026 A (ITA) LIBRERIA FELTRINELLI</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>81.20999999999999</v>
+        <v>482.7</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -969,18 +962,18 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>46031</v>
+        <v>46030</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>46032</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Disposizione - RIF:210844764 BEN. OFFICINA MECCANICA BRAMBILLA</t>
+          <t>Pagam. POS - PAGAMENTO POS 48,76 EUR DEL 08.01.2026 A (ITA) PETMARK PORTA NUOVA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>16.54</v>
+        <v>48.76</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -990,18 +983,18 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>46032</v>
+        <v>46030</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46033</v>
+        <v>46031</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Addebito SDD - DELIVEROO ITALY SRL</t>
+          <t>Disposizione - RIF:215083766 BEN. OFFICINA MECCANICA BRAMBILLA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>28.81</v>
+        <v>14.52</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1011,18 +1004,18 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>46032</v>
+        <v>46030</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46034</v>
+        <v>46030</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 79,01 EUR DEL 10.01.2026 A (ITA) TABACCHERIA N.12</t>
+          <t>Pagam. POS - PAGAMENTO POS 40,61 EUR DEL 08.01.2026 A (ITA) MALVÓN</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>79.01000000000001</v>
+        <v>40.61</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1032,18 +1025,18 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>46032</v>
+        <v>46030</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46032</v>
+        <v>46030</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 50,03 EUR DEL 10.01.2026 A (ITA) DECATHLON ASSAGO</t>
+          <t>Addebito SDD - NETFLIX INTERNATIONAL B.V.</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>50.03</v>
+        <v>14.41</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1056,15 +1049,15 @@
         <v>46032</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46034</v>
+        <v>46033</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Disposizione - RIF:214240908 BEN. TINTORIA RAPIDA CENTRO</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>13.25</v>
+          <t>RICARICA POSTEPAY DA CONTO 0123456 ORD. SOFIA ROSSI</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>195.84</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1074,18 +1067,18 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>46032</v>
+        <v>46033</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46033</v>
+        <v>46035</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 52,31 EUR DEL 10.01.2026 A (ITA) TRENITALIA S.P.A.</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 6722 UDON FIRENZE</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>52.31</v>
+        <v>17.8</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1098,15 +1091,15 @@
         <v>46033</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46035</v>
+        <v>46034</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 39,43 EUR DEL 11.01.2026 A (ITA) DECATHLON ASSAGO</t>
+          <t>Pagam. POS - PAGAMENTO POS 12,33 EUR DEL 11.01.2026 A (ITA) STAZIONE Q8</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>39.43</v>
+        <v>12.33</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1119,15 +1112,15 @@
         <v>46033</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46034</v>
+        <v>46033</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Addebito SDD - SPOTIFY AB</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 8007 CHURCH'S NORD</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.32</v>
+        <v>70.95</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -1144,11 +1137,11 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:214918412 ORD. RICARICA POSTEPAY SOFIA</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>217.28</v>
+          <t>Pagam. POS - PAGAMENTO POS 61,12 EUR DEL 11.01.2026 A (ITA) RISTORANTE DA GINO</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>61.12</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -1158,18 +1151,18 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>46034</v>
+        <v>46033</v>
       </c>
       <c r="B44" s="2" t="n">
         <v>46034</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 83,26 EUR DEL 12.01.2026 A (ITA) DECATHLON ASSAGO</t>
+          <t>Addebito SDD - NETFLIX INTERNATIONAL B.V.</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>83.26000000000001</v>
+        <v>11.8</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -1179,18 +1172,18 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>46036</v>
+        <v>46033</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46036</v>
+        <v>46034</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 1735 TRATTORIA LA PERGOLA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>79.13</v>
+          <t>RICARICA POSTEPAY DA CONTO 0123456 ORD. SOFIA ROSSI</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>77.29000000000001</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -1200,18 +1193,18 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>46036</v>
+        <v>46034</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46036</v>
+        <v>46034</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Disposizione - RIF:210233615 BEN. UNIVERSITA' DEGLI STUDI DI BOLOGNA</t>
+          <t>Pagam. POS - PAGAMENTO POS 10,94 EUR DEL 12.01.2026 A (ITA) ESSELUNGA MILANO</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>332.69</v>
+        <v>10.94</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -1221,18 +1214,18 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>46036</v>
+        <v>46034</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46036</v>
+        <v>46034</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Addebito SDD - MENSA SCOLASTICA COMUNE DI MILANO</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 2119 WYCON COSMETICS</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>54.45</v>
+        <v>45.58</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -1242,18 +1235,18 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>46036</v>
+        <v>46034</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46036</v>
+        <v>46035</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:212722426 ORD. RICARICA POSTEPAY SOFIA</t>
+          <t>RICARICA POSTEPAY DA CONTO 0123456 ORD. SOFIA ROSSI</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>291</v>
+        <v>56.24</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -1263,18 +1256,18 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B49" s="2" t="n">
         <v>46037</v>
       </c>
-      <c r="B49" s="2" t="n">
-        <v>46038</v>
-      </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 5964 CONAD SUPERSTORE</t>
+          <t>Pagam. POS - PAGAMENTO POS 133,12 EUR DEL 13.01.2026 A (ITA) DECATHLON ASSAGO</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>54.68</v>
+        <v>133.12</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -1284,18 +1277,18 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>46037</v>
+        <v>46035</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46039</v>
+        <v>46035</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 74,17 EUR DEL 15.01.2026 A (ITA) CALZEDONIA GROUP</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 2342 OVS S.P.A.</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>74.17</v>
+        <v>101.31</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -1305,18 +1298,18 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
+        <v>46036</v>
+      </c>
+      <c r="B51" s="2" t="n">
         <v>46037</v>
       </c>
-      <c r="B51" s="2" t="n">
-        <v>46039</v>
-      </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 67,24 EUR DEL 15.01.2026 A (ITA) MACELLERIA BONI</t>
+          <t>Addebito SDD - APPLE.COM/BILL</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>67.23999999999999</v>
+        <v>6.59</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -1326,18 +1319,18 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>46037</v>
+        <v>46036</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:218350868 ORD. RICARICA POSTEPAY SOFIA</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>241.27</v>
+          <t>Pagam. POS - PAGAMENTO POS 15,90 EUR DEL 14.01.2026 A (ITA) MEGA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>15.9</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -1347,18 +1340,18 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>46038</v>
+        <v>46036</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46038</v>
+        <v>46036</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 62,88 EUR DEL 16.01.2026 A (ITA) RISTORANTE DA GINO</t>
+          <t>Disposizione - RIF:214212237 BEN. UNIVERSITA' DEGLI STUDI DI BOLOGNA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>62.88</v>
+        <v>332.69</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -1368,18 +1361,18 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>46038</v>
+        <v>46037</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46038</v>
+        <v>46037</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 31,49 EUR DEL 16.01.2026 A (ITA) PESCHERIA DEL PORTO</t>
+          <t>Pagam. POS - PAGAMENTO POS 59,41 EUR DEL 15.01.2026 A (ITA) DISTRIBUTORE ENI</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>31.49</v>
+        <v>59.41</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -1392,15 +1385,15 @@
         <v>46038</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46040</v>
+        <v>46038</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Addebito SDD - MENSA SCOLASTICA COMUNE DI MILANO</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 8771 FAMILA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>763.1799999999999</v>
+        <v>143.41</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -1413,15 +1406,15 @@
         <v>46038</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46038</v>
+        <v>46039</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:211865074 ORD. RICARICA POSTEPAY SOFIA</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>130.24</v>
+          <t>Pagam. POS - PAGAMENTO POS 28,60 EUR DEL 16.01.2026 A (ITA) PITAYA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>28.6</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -1438,11 +1431,11 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 15,64 EUR DEL 17.01.2026 A (ITA) ITALO NTV S.P.A.</t>
+          <t>Addebito SDD - MENSA SCOLASTICA COMUNE DI MILANO</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>15.64</v>
+        <v>669.22</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -1452,18 +1445,18 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>46041</v>
+        <v>46039</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46041</v>
+        <v>46039</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Addebito SDD - JUST EAT ITALY SRL</t>
+          <t>Addebito SDD - NETFLIX INTERNATIONAL B.V.</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>59.78</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -1473,18 +1466,18 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>46041</v>
+        <v>46039</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46041</v>
+        <v>46040</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 153,75 EUR DEL 19.01.2026 A (ITA) PESCHERIA DEL PORTO</t>
+          <t>Disposizione - RIF:213457963 BEN. TINTORIA RAPIDA CENTRO</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>153.75</v>
+        <v>92.92</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -1494,18 +1487,18 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>46041</v>
+        <v>46040</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46043</v>
+        <v>46042</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Addebito SDD - DELIVEROO ITALY SRL</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 3236 100 MONTADITOS</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>18.62</v>
+        <v>58.69</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -1515,18 +1508,18 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>46041</v>
+        <v>46040</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46043</v>
+        <v>46042</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 9,49 EUR DEL 19.01.2026 A (ITA) MEDIAWORLD CARUGATE</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 7512 TUODÌ CINISELLO BALSAMO</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>9.49</v>
+        <v>157.53</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -1536,18 +1529,18 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
+        <v>46040</v>
+      </c>
+      <c r="B62" s="2" t="n">
         <v>46041</v>
       </c>
-      <c r="B62" s="2" t="n">
-        <v>46043</v>
-      </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 8429 TRATTORIA LA PERGOLA</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>64.5</v>
+          <t>Bonif. v/fav. - RIF:216024535 ORD. RICARICA POSTEPAY SOFIA</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>256.79</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -1560,15 +1553,15 @@
         <v>46041</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46041</v>
+        <v>46043</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>RICARICA POSTEPAY DA CONTO 0123456 ORD. SOFIA ROSSI</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>225.7</v>
+          <t>Disposizione - RIF:215112575 BEN. TINTORIA RAPIDA CENTRO</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>33.69</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -1585,11 +1578,11 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:213697541 ORD. RICARICA POSTEPAY SOFIA</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>175.85</v>
+          <t>Pagam. POS - PAGAMENTO POS 59,78 EUR DEL 19.01.2026 A (ITA) FIVE GUYS</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>59.78</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -1599,18 +1592,18 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>46042</v>
+        <v>46041</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46042</v>
+        <v>46041</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 24,59 EUR DEL 20.01.2026 A (ITA) RISTORANTE DA GINO</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 1496 CONAD OSTIENSE</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>24.59</v>
+        <v>153.75</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -1620,18 +1613,18 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>46042</v>
+        <v>46041</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46042</v>
+        <v>46041</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Addebito SDD - SPOTIFY AB</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 9465 IKEA RESTAURANT</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>12.41</v>
+        <v>18.62</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -1641,10 +1634,10 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>46042</v>
+        <v>46041</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46042</v>
+        <v>46041</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -1652,7 +1645,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>234.65</v>
+        <v>95.92</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -1662,18 +1655,18 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>46043</v>
+        <v>46042</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46045</v>
+        <v>46044</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 15,82 EUR DEL 21.01.2026 A (ITA) ZARA ITALIA SRL</t>
+          <t>PRELIEVO ATM BANCOMAT FIL. 00456 MILANO</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>15.82</v>
+        <v>26.33</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -1683,18 +1676,18 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>46043</v>
+        <v>46042</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46045</v>
+        <v>46042</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 18,49 EUR DEL 21.01.2026 A (ITA) LIDL ITALIA SRL</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>18.49</v>
+          <t>RICARICA POSTEPAY DA CONTO 0123456 ORD. SOFIA ROSSI</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>151.77</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -1707,15 +1700,15 @@
         <v>46043</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>46043</v>
+        <v>46045</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 6039 ESSELUNGA S.P.A.</t>
+          <t>Addebito SDD - NETFLIX INTERNATIONAL B.V.</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>156.62</v>
+        <v>13.09</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -1725,18 +1718,18 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>RICARICA POSTEPAY DA CONTO 0123456 ORD. SOFIA ROSSI</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>233.95</v>
+          <t>AMAZON.IT MARKETPLACE - ORDINE 402-212609726</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10.05</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -1753,11 +1746,11 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 7131 TRATTORIA LA PERGOLA</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 2590 AUTOGRILL</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>81.38</v>
+        <v>58.06</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -1770,15 +1763,15 @@
         <v>46044</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>46046</v>
+        <v>46045</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 57,97 EUR DEL 22.01.2026 A (ITA) DISTRIBUTORE ENI</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 8984 ESSELUNGA S.P.A.</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>57.97</v>
+        <v>156.05</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -1795,11 +1788,11 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 8826 TRATTORIA LA PERGOLA</t>
+          <t>Pagam. POS - PAGAMENTO POS 169,03 EUR DEL 23.01.2026 A (ITA) PANIFICIO TOSI</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>53.9</v>
+        <v>169.03</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -1816,11 +1809,11 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 24,36 EUR DEL 23.01.2026 A (ITA) RISTORANTE DA GINO</t>
+          <t>Pagam. POS - PAGAMENTO POS 26,16 EUR DEL 23.01.2026 A (ITA) DOPPIO MALTO</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>24.36</v>
+        <v>26.16</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -1830,18 +1823,18 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 143,85 EUR DEL 23.01.2026 A (ITA) CONAD CITY ROMA</t>
+          <t>Pagam. POS - PAGAMENTO POS 21,44 EUR DEL 24.01.2026 A (ITA) IPER</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>143.85</v>
+        <v>21.44</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -1851,18 +1844,18 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>46045</v>
+        <v>46047</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>46045</v>
+        <v>46049</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 26,16 EUR DEL 23.01.2026 A (ITA) BAR CENTRALE</t>
+          <t>Pagam. POS - PAGAMENTO POS 98,44 EUR DEL 25.01.2026 A (ITA) MEGA TIBURTINA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>26.16</v>
+        <v>98.44</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -1872,18 +1865,18 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 54,20 EUR DEL 24.01.2026 A (ITA) ROSTICCERIA DA MARIO</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>54.2</v>
+          <t>RICARICA POSTEPAY DA CONTO 0123456 ORD. SOFIA ROSSI</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>82.84999999999999</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -1893,18 +1886,18 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>46046</v>
+        <v>46048</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>46046</v>
+        <v>46049</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Addebito SDD - SPOTIFY AB</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 8725 SUSHIKO</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>5.14</v>
+        <v>81.52</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -1914,18 +1907,18 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>46046</v>
+        <v>46049</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>46047</v>
+        <v>46049</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>RICARICA POSTEPAY DA CONTO 0123456 ORD. SOFIA ROSSI</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
-        <v>294.81</v>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 2023 MONDADORI</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>676.3200000000001</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -1935,18 +1928,18 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>46046</v>
+        <v>46049</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>46047</v>
+        <v>46051</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:210765283 ORD. RICARICA POSTEPAY SOFIA</t>
-        </is>
-      </c>
-      <c r="E81" t="n">
-        <v>88.69</v>
+          <t>Disposizione - RIF:219557439 BEN. OFFICINA MECCANICA BRAMBILLA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>38.25</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -1956,18 +1949,18 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>46047</v>
+        <v>46049</v>
       </c>
       <c r="B82" s="2" t="n">
         <v>46049</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 117,27 EUR DEL 25.01.2026 A (ITA) H&amp;M HENNES AND MAURITZ</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>117.27</v>
+          <t>Bonif. v/fav. - RIF:213768989 ORD. RICARICA POSTEPAY SOFIA</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>128.95</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -1977,10 +1970,10 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>46047</v>
+        <v>46049</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>46047</v>
+        <v>46049</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -1988,7 +1981,7 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>51.1</v>
+        <v>212.89</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -1998,18 +1991,18 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>46047</v>
+        <v>46050</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>46048</v>
+        <v>46051</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:219228299 ORD. RICARICA POSTEPAY SOFIA</t>
-        </is>
-      </c>
-      <c r="E84" t="n">
-        <v>229.92</v>
+          <t>Pagam. POS - PAGAMENTO POS 24,55 EUR DEL 28.01.2026 A (ITA) BAR CENTRALE</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>24.55</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -2019,18 +2012,18 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 69,70 EUR DEL 26.01.2026 A (ITA) ZARA ITALIA SRL</t>
+          <t>Pagam. POS - PAGAMENTO POS 66,45 EUR DEL 28.01.2026 A (ITA) ALL'ANTICO VINAIO MILANO</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>69.7</v>
+        <v>66.45</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -2040,18 +2033,18 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>46048</v>
+        <v>46051</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>46048</v>
+        <v>46051</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>RICARICA POSTEPAY DA CONTO 0123456 ORD. SOFIA ROSSI</t>
-        </is>
-      </c>
-      <c r="E86" t="n">
-        <v>107.77</v>
+          <t>Pagam. POS - PAGAMENTO POS 20,13 EUR DEL 29.01.2026 A (ITA) ITALO NTV S.P.A.</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>20.13</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -2061,18 +2054,18 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>46049</v>
+        <v>46051</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>46049</v>
+        <v>46051</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 81,67 EUR DEL 27.01.2026 A (ITA) RISTORANTE DA GINO</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 6626 SIGMA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>81.67</v>
+        <v>43.11</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -2082,18 +2075,18 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>46049</v>
+        <v>46051</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>46049</v>
+        <v>46051</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 6,88 EUR DEL 27.01.2026 A (ITA) PIZZERIA NAPOLI</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 8077 CONAD SUPERSTORE</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>6.88</v>
+        <v>176.34</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -2103,18 +2096,18 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 119,27 EUR DEL 28.01.2026 A (ITA) CALZEDONIA GROUP</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>119.27</v>
+          <t>RICARICA POSTEPAY DA CONTO 0123456 ORD. SOFIA ROSSI</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>64.02</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -2124,18 +2117,18 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>46050</v>
+        <v>46052</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>46050</v>
+        <v>46053</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 93,95 EUR DEL 28.01.2026 A (ITA) COOP LOMBARDIA</t>
+          <t>Pagam. POS - PAGAMENTO POS 19,54 EUR DEL 30.01.2026 A (ITA) KEBHOUZE GENOVA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>93.95</v>
+        <v>19.54</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -2145,18 +2138,18 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>46051</v>
+        <v>46054</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Addebito SDD - TELECOM ITALIA S.P.A. FIBRA</t>
+          <t>Pagam. POS - PAGAMENTO POS 14,72 EUR DEL 30.01.2026 A (ITA) PENNY</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>90.38</v>
+        <v>14.72</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -2173,11 +2166,11 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Addebito SDD - MENSA SCOLASTICA COMUNE DI MILANO</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 3255 MONDADORI</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>769.53</v>
+        <v>588.9400000000001</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -2190,15 +2183,15 @@
         <v>46052</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>46052</v>
+        <v>46054</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 73,25 EUR DEL 30.01.2026 A (ITA) ESSELUNGA MILANO</t>
+          <t>Pagam. POS - PAGAMENTO POS 6,15 EUR DEL 30.01.2026 A (ITA) UNIEURO S.P.A.</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>73.25</v>
+        <v>6.15</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -2208,18 +2201,18 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>46053</v>
+        <v>46052</v>
       </c>
       <c r="B94" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Addebito SDD - SARA ASSICURAZIONI RCA AUTO</t>
+          <t>Pagam. POS - PAGAMENTO POS 121,59 EUR DEL 30.01.2026 A (ITA) LA FELTRINELLI BRESCIA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>40.8</v>
+        <v>121.59</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -2236,11 +2229,11 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Disposizione - RIF:212391341 BEN. UNIVERSITA' DEGLI STUDI DI BOLOGNA</t>
+          <t>Addebito SDD - NETFLIX INTERNATIONAL B.V.</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>709.41</v>
+        <v>7.44</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -2250,18 +2243,18 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>46054</v>
+        <v>46053</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>46056</v>
+        <v>46053</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>AMAZON.IT MARKETPLACE - ORDINE 402-215646529</t>
+          <t>Addebito SDD - SARA ASSICURAZIONI RCA AUTO</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>13.33</v>
+        <v>40.8</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -2271,18 +2264,18 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>46054</v>
+        <v>46053</v>
       </c>
       <c r="B97" s="2" t="n">
         <v>46054</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 72,36 EUR DEL 01.02.2026 A (ITA) BAR CENTRALE</t>
+          <t>Addebito SDD - MENSA SCOLASTICA COMUNE DI MILANO</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>72.36</v>
+        <v>652.55</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -2299,11 +2292,11 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 25,89 EUR DEL 01.02.2026 A (ITA) TRENITALIA S.P.A.</t>
+          <t>AMAZON.IT MARKETPLACE - ORDINE 402-215150496</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>25.89</v>
+        <v>5.21</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -2313,18 +2306,18 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:212051509 ORD. RICARICA POSTEPAY SOFIA</t>
-        </is>
-      </c>
-      <c r="E99" t="n">
-        <v>263.88</v>
+          <t>Pagam. POS - PAGAMENTO POS 734,87 EUR DEL 02.02.2026 A (ITA) UBIK</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>734.87</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -2337,15 +2330,15 @@
         <v>46055</v>
       </c>
       <c r="B100" s="2" t="n">
-        <v>46056</v>
+        <v>46055</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 105,10 EUR DEL 02.02.2026 A (ITA) CONAD CITY ROMA</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 1988 FUNSIDE PARMA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>105.1</v>
+        <v>580.6900000000001</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -2355,18 +2348,18 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Addebito SDD - WIND TRE S.P.A. MOBILE</t>
+          <t>Pagam. POS - PAGAMENTO POS 45,46 EUR DEL 03.02.2026 A (ITA) CARREFOUR CONTACT BRESCIA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>87.87</v>
+        <v>45.46</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -2376,18 +2369,18 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 135,61 EUR DEL 03.02.2026 A (ITA) PESCHERIA DEL PORTO</t>
+          <t>Pagam. POS - PAGAMENTO POS 27,54 EUR DEL 04.02.2026 A (ITA) STARBUCKS RESERVE</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>135.61</v>
+        <v>27.54</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -2397,18 +2390,18 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B103" s="2" t="n">
         <v>46057</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 9,23 EUR DEL 03.02.2026 A (ITA) UNIEURO S.P.A.</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 4721 WOK TO WALK</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>9.23</v>
+        <v>60.8</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -2418,18 +2411,18 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
+        <v>46057</v>
+      </c>
+      <c r="B104" s="2" t="n">
         <v>46058</v>
       </c>
-      <c r="B104" s="2" t="n">
-        <v>46060</v>
-      </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 64,21 EUR DEL 05.02.2026 A (ITA) STAZIONE Q8</t>
+          <t>Addebito SDD - NETFLIX INTERNATIONAL B.V.</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>64.20999999999999</v>
+        <v>11.92</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -2439,18 +2432,18 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="B105" s="2" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 31,73 EUR DEL 05.02.2026 A (ITA) ESSELUNGA MILANO</t>
+          <t>Pagam. POS - PAGAMENTO POS 151,37 EUR DEL 04.02.2026 A (ITA) COOP.FI</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>31.73</v>
+        <v>151.37</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -2460,18 +2453,18 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 71,62 EUR DEL 05.02.2026 A (ITA) TABACCHERIA N.12</t>
+          <t>Disposizione - RIF:215342149 BEN. UNIVERSITA' DEGLI STUDI DI BOLOGNA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>71.62</v>
+        <v>604.42</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -2481,18 +2474,18 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>46058</v>
+        <v>46057</v>
       </c>
       <c r="B107" s="2" t="n">
         <v>46058</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>RICARICA POSTEPAY DA CONTO 0123456 ORD. SOFIA ROSSI</t>
-        </is>
-      </c>
-      <c r="E107" t="n">
-        <v>73.37</v>
+          <t>Pagam. POS - PAGAMENTO POS 68,81 EUR DEL 04.02.2026 A (ITA) PIZZERIA NAPOLI</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>68.81</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -2502,18 +2495,18 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>46059</v>
+        <v>46057</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>46059</v>
+        <v>46057</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Addebito SDD - DELIVEROO ITALY SRL</t>
+          <t>Pagam. POS - PAGAMENTO POS 8,21 EUR DEL 04.02.2026 A (ITA) UNIEURO S.P.A.</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>53.58</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -2523,18 +2516,18 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>46060</v>
+        <v>46057</v>
       </c>
       <c r="B109" s="2" t="n">
-        <v>46062</v>
+        <v>46058</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 306,01 EUR DEL 07.02.2026 A (ITA) LIBRERIA FELTRINELLI</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>306.01</v>
+          <t>RICARICA POSTEPAY DA CONTO 0123456 ORD. SOFIA ROSSI</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>52.49</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -2544,18 +2537,18 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>46060</v>
+        <v>46057</v>
       </c>
       <c r="B110" s="2" t="n">
-        <v>46060</v>
+        <v>46058</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Disposizione - RIF:211500390 BEN. TINTORIA RAPIDA CENTRO</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>24.73</v>
+          <t>RICARICA POSTEPAY DA CONTO 0123456 ORD. SOFIA ROSSI</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>92.68000000000001</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -2565,18 +2558,18 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>46060</v>
+        <v>46058</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>46061</v>
+        <v>46058</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>RICARICA POSTEPAY DA CONTO 0123456 ORD. SOFIA ROSSI</t>
-        </is>
-      </c>
-      <c r="E111" t="n">
-        <v>247.34</v>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 3754 MERCATÒ EXTRA ROMA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>11.42</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -2586,18 +2579,18 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>46061</v>
+        <v>46058</v>
       </c>
       <c r="B112" s="2" t="n">
-        <v>46061</v>
+        <v>46060</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 148,34 EUR DEL 08.02.2026 A (ITA) PESCHERIA DEL PORTO</t>
+          <t>Pagam. POS - PAGAMENTO POS 64,21 EUR DEL 05.02.2026 A (ITA) STAZIONE Q8</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>148.34</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -2607,18 +2600,18 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>46061</v>
+        <v>46058</v>
       </c>
       <c r="B113" s="2" t="n">
-        <v>46063</v>
+        <v>46059</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 139,53 EUR DEL 08.02.2026 A (ITA) DECATHLON ASSAGO</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>139.53</v>
+          <t>RICARICA POSTEPAY DA CONTO 0123456 ORD. SOFIA ROSSI</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>168.49</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -2628,18 +2621,18 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>46062</v>
+        <v>46059</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>46062</v>
+        <v>46061</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>RICARICA POSTEPAY DA CONTO 0123456 ORD. SOFIA ROSSI</t>
-        </is>
-      </c>
-      <c r="E114" t="n">
-        <v>111.48</v>
+          <t>Disposizione - RIF:211338593 BEN. UNIVERSITA' DEGLI STUDI DI BOLOGNA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>207.92</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -2649,18 +2642,18 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>46063</v>
+        <v>46060</v>
       </c>
       <c r="B115" s="2" t="n">
-        <v>46063</v>
+        <v>46060</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Disposizione - RIF:215733093 BEN. AFFITTO APPARTAMENTO SOFIA BOLOGNA</t>
+          <t>Pagam. POS - PAGAMENTO POS 26,87 EUR DEL 07.02.2026 A (ITA) PENNY</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>38.3</v>
+        <v>26.87</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -2670,18 +2663,18 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>46063</v>
+        <v>46060</v>
       </c>
       <c r="B116" s="2" t="n">
-        <v>46065</v>
+        <v>46060</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 33,25 EUR DEL 10.02.2026 A (ITA) PIZZERIA NAPOLI</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 5345 PITAYA PORTA NUOVA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>33.25</v>
+        <v>47.91</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -2691,18 +2684,18 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>46064</v>
+        <v>46060</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>46065</v>
+        <v>46061</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Addebito SDD - ACI BOLLO AUTO TARGA YE247JV</t>
+          <t>Addebito SDD - GOOGLE *CLOUD STORAGE</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>15.99</v>
+        <v>12.89</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -2712,18 +2705,18 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>46064</v>
+        <v>46061</v>
       </c>
       <c r="B118" s="2" t="n">
-        <v>46064</v>
+        <v>46062</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 76,34 EUR DEL 11.02.2026 A (ITA) LIDL ITALIA SRL</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>76.34</v>
+          <t>Bonif. v/fav. - RIF:213966900 ORD. RICARICA POSTEPAY SOFIA</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>244.86</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -2733,18 +2726,18 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>46064</v>
+        <v>46062</v>
       </c>
       <c r="B119" s="2" t="n">
         <v>46064</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 163,57 EUR DEL 11.02.2026 A (ITA) PANIFICIO TOSI</t>
+          <t>Pagam. POS - PAGAMENTO POS 287,01 EUR DEL 09.02.2026 A (ITA) MONDADORI CORSICO</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>163.57</v>
+        <v>287.01</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -2754,18 +2747,18 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>46065</v>
+        <v>46063</v>
       </c>
       <c r="B120" s="2" t="n">
-        <v>46066</v>
+        <v>46063</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 12,64 EUR DEL 12.02.2026 A (ITA) TRENITALIA S.P.A.</t>
+          <t>Pagam. POS - PAGAMENTO POS 40,33 EUR DEL 10.02.2026 A (ITA) GABOR</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>12.64</v>
+        <v>40.33</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -2775,18 +2768,18 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>46065</v>
+        <v>46064</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>46065</v>
+        <v>46064</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 64,98 EUR DEL 12.02.2026 A (ITA) PIZZERIA NAPOLI</t>
+          <t>Pagam. POS - PAGAMENTO POS 22,40 EUR DEL 11.02.2026 A (ITA) CONAD CITY ROMA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>64.98</v>
+        <v>22.4</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -2796,18 +2789,18 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>46067</v>
+        <v>46064</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>46067</v>
+        <v>46065</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 93,10 EUR DEL 14.02.2026 A (ITA) PESCHERIA DEL PORTO</t>
+          <t>Pagam. POS - PAGAMENTO POS 67,69 EUR DEL 11.02.2026 A (ITA) ARCAPLANET PERUGIA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>93.09999999999999</v>
+        <v>67.69</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -2817,18 +2810,18 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>46067</v>
+        <v>46065</v>
       </c>
       <c r="B123" s="2" t="n">
-        <v>46068</v>
+        <v>46065</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 32,13 EUR DEL 14.02.2026 A (ITA) COOP LOMBARDIA</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 7131 TIGOTÀ</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>32.13</v>
+        <v>61.3</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -2838,10 +2831,10 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>46067</v>
+        <v>46066</v>
       </c>
       <c r="B124" s="2" t="n">
-        <v>46067</v>
+        <v>46066</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -2849,7 +2842,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>7.58</v>
+        <v>13.1</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -2859,18 +2852,18 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B125" s="2" t="n">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>PRELIEVO ATM BANCOMAT FIL. 00456 MILANO</t>
+          <t>Pagam. POS - PAGAMENTO POS 50,68 EUR DEL 15.02.2026 A (ITA) BAR CENTRALE</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>79.40000000000001</v>
+        <v>50.68</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -2880,18 +2873,18 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B126" s="2" t="n">
-        <v>46068</v>
+        <v>46070</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 93,38 EUR DEL 14.02.2026 A (ITA) CONAD CITY ROMA</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 2633 CONAD SUPERSTORE</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>93.38</v>
+        <v>126.7</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -2901,18 +2894,18 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B127" s="2" t="n">
-        <v>46070</v>
+        <v>46069</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Addebito SDD - MENSA SCOLASTICA COMUNE DI MILANO</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 7666 TUODÌ CATANIA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>192.96</v>
+        <v>134.49</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -2929,11 +2922,11 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Addebito SDD - SPOTIFY AB</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>11.51</v>
+          <t>RICARICA POSTEPAY DA CONTO 0123456 ORD. SOFIA ROSSI</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>67.52</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -2946,15 +2939,15 @@
         <v>46069</v>
       </c>
       <c r="B129" s="2" t="n">
-        <v>46069</v>
+        <v>46070</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 134,49 EUR DEL 16.02.2026 A (ITA) MACELLERIA BONI</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>134.49</v>
+          <t>Bonif. v/fav. - RIF:219328175 ORD. RICARICA POSTEPAY SOFIA</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>113.82</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -2964,18 +2957,18 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>46069</v>
+        <v>46070</v>
       </c>
       <c r="B130" s="2" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Addebito SDD - TELEPASS S.P.A. PEDAGGI</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>41.53</v>
+          <t>Bonif. v/fav. - RIF:216540556 ORD. RICARICA POSTEPAY SOFIA</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>271.15</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -2985,18 +2978,18 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>46069</v>
+        <v>46070</v>
       </c>
       <c r="B131" s="2" t="n">
         <v>46070</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 11,24 EUR DEL 16.02.2026 A (ITA) UNIEURO S.P.A.</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>11.24</v>
+          <t>Bonif. v/fav. - RIF:218321129 ORD. RICARICA POSTEPAY SOFIA</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>248.09</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -3006,18 +2999,18 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B132" s="2" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Addebito SDD - DELIVEROO ITALY SRL</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 8901 TRATTORIA LA PERGOLA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>8.68</v>
+        <v>63.9</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -3027,18 +3020,18 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B133" s="2" t="n">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 50,85 EUR DEL 17.02.2026 A (ITA) LIDL ITALIA SRL</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 6384 SNIPES PARMA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>50.85</v>
+        <v>51.4</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -3048,18 +3041,18 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>46070</v>
+        <v>46072</v>
       </c>
       <c r="B134" s="2" t="n">
-        <v>46070</v>
+        <v>46072</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 3663 OVS S.P.A.</t>
+          <t>Pagam. POS - PAGAMENTO POS 81,68 EUR DEL 19.02.2026 A (ITA) ROSTICCERIA DA MARIO</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>79.69</v>
+        <v>81.68000000000001</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -3069,18 +3062,18 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>46070</v>
+        <v>46072</v>
       </c>
       <c r="B135" s="2" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Disposizione - RIF:216614267 BEN. UNIVERSITA' DEGLI STUDI DI BOLOGNA</t>
+          <t>Pagam. POS - PAGAMENTO POS 13,69 EUR DEL 19.02.2026 A (ITA) MCDONALD'S ITALIA</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>548.3200000000001</v>
+        <v>13.69</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -3093,15 +3086,15 @@
         <v>46072</v>
       </c>
       <c r="B136" s="2" t="n">
-        <v>46073</v>
+        <v>46074</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 1076 TRATTORIA LA PERGOLA</t>
+          <t>Addebito SDD - SARA ASSICURAZIONI RCA AUTO</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>57.01</v>
+        <v>43.61</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -3114,15 +3107,15 @@
         <v>46072</v>
       </c>
       <c r="B137" s="2" t="n">
-        <v>46073</v>
+        <v>46074</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Addebito SDD - ACI BOLLO AUTO TARGA DR372GA</t>
+          <t>Addebito SDD - GENERALI ITALIA POLIZZA VITA</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>29.42</v>
+        <v>49.87</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -3132,18 +3125,18 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B138" s="2" t="n">
         <v>46074</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 120,05 EUR DEL 19.02.2026 A (ITA) ZARA ITALIA SRL</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 1162 TRATTORIA LA PERGOLA</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>120.05</v>
+        <v>53.39</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -3153,18 +3146,18 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>46072</v>
+        <v>46074</v>
       </c>
       <c r="B139" s="2" t="n">
-        <v>46074</v>
+        <v>46076</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Addebito SDD - SPOTIFY AB</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 3472 MD</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>10.76</v>
+        <v>111.99</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -3174,18 +3167,18 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>46073</v>
+        <v>46074</v>
       </c>
       <c r="B140" s="2" t="n">
-        <v>46073</v>
+        <v>46074</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 61,08 EUR DEL 20.02.2026 A (ITA) ITALO NTV S.P.A.</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>61.08</v>
+          <t>RICARICA POSTEPAY DA CONTO 0123456 ORD. SOFIA ROSSI</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>56.5</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -3195,18 +3188,18 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>46073</v>
+        <v>46075</v>
       </c>
       <c r="B141" s="2" t="n">
-        <v>46073</v>
+        <v>46075</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 93,91 EUR DEL 20.02.2026 A (ITA) ZARA ITALIA SRL</t>
+          <t>Pagam. POS - PAGAMENTO POS 36,94 EUR DEL 22.02.2026 A (ITA) ALICE</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>93.91</v>
+        <v>36.94</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -3216,18 +3209,18 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>46073</v>
+        <v>46075</v>
       </c>
       <c r="B142" s="2" t="n">
-        <v>46073</v>
+        <v>46075</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Disposizione - RIF:219554279 BEN. UNIVERSITA' DEGLI STUDI DI BOLOGNA</t>
+          <t>Addebito SDD - SARA ASSICURAZIONI RCA AUTO</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>102.82</v>
+        <v>24.28</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -3237,18 +3230,18 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B143" s="2" t="n">
-        <v>46074</v>
+        <v>46077</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 7,87 EUR DEL 20.02.2026 A (ITA) UNIEURO S.P.A.</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 9156 UBIK MARGHERA</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>7.87</v>
+        <v>671.9</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -3258,18 +3251,18 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>46073</v>
+        <v>46077</v>
       </c>
       <c r="B144" s="2" t="n">
-        <v>46073</v>
+        <v>46078</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:218397018 ORD. RICARICA POSTEPAY SOFIA</t>
-        </is>
-      </c>
-      <c r="E144" t="n">
-        <v>166.38</v>
+          <t>Pagam. POS - PAGAMENTO POS 10,07 EUR DEL 24.02.2026 A (ITA) MEDIAWORLD CARUGATE</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>10.07</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -3279,18 +3272,18 @@
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>46074</v>
+        <v>46077</v>
       </c>
       <c r="B145" s="2" t="n">
-        <v>46074</v>
+        <v>46079</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:215981200 ORD. RICARICA POSTEPAY SOFIA</t>
-        </is>
-      </c>
-      <c r="E145" t="n">
-        <v>220.56</v>
+          <t>Pagam. POS - PAGAMENTO POS 463,22 EUR DEL 24.02.2026 A (ITA) BUCHHANDLUNG WALTHER KÖNIG</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>463.22</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -3300,18 +3293,18 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B146" s="2" t="n">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 10,07 EUR DEL 23.02.2026 A (ITA) MEDIAWORLD CARUGATE</t>
+          <t>Pagam. POS - PAGAMENTO POS 28,02 EUR DEL 24.02.2026 A (ITA) ITALO NTV S.P.A.</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>10.07</v>
+        <v>28.02</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -3321,18 +3314,18 @@
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>46076</v>
+        <v>46078</v>
       </c>
       <c r="B147" s="2" t="n">
-        <v>46076</v>
+        <v>46078</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 17,37 EUR DEL 23.02.2026 A (ITA) MCDONALD'S ITALIA</t>
+          <t>Pagam. POS - PAGAMENTO POS 73,78 EUR DEL 25.02.2026 A (ITA) HOKA</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>17.37</v>
+        <v>73.78</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -3342,18 +3335,18 @@
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>46076</v>
+        <v>46078</v>
       </c>
       <c r="B148" s="2" t="n">
-        <v>46076</v>
+        <v>46079</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 7868 OVS S.P.A.</t>
+          <t>Addebito SDD - DELIVEROO ITALY SRL</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>45.6</v>
+        <v>47.31</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -3363,18 +3356,18 @@
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B149" s="2" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 9,67 EUR DEL 24.02.2026 A (ITA) CONAD CITY ROMA</t>
+          <t>Addebito SDD - GOOGLE *CLOUD STORAGE</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>9.67</v>
+        <v>14.65</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -3384,18 +3377,18 @@
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B150" s="2" t="n">
-        <v>46079</v>
+        <v>46078</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 13,77 EUR DEL 24.02.2026 A (ITA) COOP LOMBARDIA</t>
+          <t>Pagam. POS - PAGAMENTO POS 81,14 EUR DEL 25.02.2026 A (ITA) ESSELUNGA COLOGNO MONZESE</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>13.77</v>
+        <v>81.14</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -3405,18 +3398,18 @@
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B151" s="2" t="n">
-        <v>46077</v>
+        <v>46080</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 51,39 EUR DEL 24.02.2026 A (ITA) CALZEDONIA GROUP</t>
+          <t>Pagam. POS - PAGAMENTO POS 62,21 EUR DEL 25.02.2026 A (ITA) TODIS MARGHERA</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>51.39</v>
+        <v>62.21</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -3426,18 +3419,18 @@
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="B152" s="2" t="n">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:217921527 ORD. RICARICA POSTEPAY SOFIA</t>
-        </is>
-      </c>
-      <c r="E152" t="n">
-        <v>114.9</v>
+          <t>Pagam. POS - PAGAMENTO POS 22,96 EUR DEL 26.02.2026 A (ITA) ITALO NTV S.P.A.</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>22.96</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -3447,18 +3440,18 @@
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="B153" s="2" t="n">
-        <v>46078</v>
+        <v>46081</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>RICARICA POSTEPAY DA CONTO 0123456 ORD. SOFIA ROSSI</t>
-        </is>
-      </c>
-      <c r="E153" t="n">
-        <v>61.71</v>
+          <t>Addebito SDD - APPLE.COM/BILL</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>11.3</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -3468,18 +3461,18 @@
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B154" s="2" t="n">
-        <v>46080</v>
+        <v>46079</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Addebito SDD - DELIVEROO ITALY SRL</t>
+          <t>Pagam. POS - PAGAMENTO POS 60,51 EUR DEL 26.02.2026 A (ITA) BAR CENTRALE</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>70.45</v>
+        <v>60.51</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -3496,11 +3489,11 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 136,25 EUR DEL 26.02.2026 A (ITA) LIDL ITALIA SRL</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>136.25</v>
+          <t>RICARICA POSTEPAY DA CONTO 0123456 ORD. SOFIA ROSSI</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>143.96</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -3510,18 +3503,18 @@
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B156" s="2" t="n">
         <v>46080</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:217056683 ORD. RICARICA POSTEPAY SOFIA</t>
-        </is>
-      </c>
-      <c r="E156" t="n">
-        <v>278.02</v>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 5170 FUNSIDE OSTIENSE</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>614.99</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -3534,15 +3527,15 @@
         <v>46080</v>
       </c>
       <c r="B157" s="2" t="n">
-        <v>46082</v>
+        <v>46081</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 3682 LIDL ITALIA</t>
+          <t>Addebito SDD - APPLE.COM/BILL</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>48.24</v>
+        <v>13.38</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -3555,15 +3548,15 @@
         <v>46080</v>
       </c>
       <c r="B158" s="2" t="n">
-        <v>46082</v>
+        <v>46081</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Addebito SDD - GOOGLE *CLOUD STORAGE</t>
+          <t>Pagam. POS - PAGAMENTO POS 26,03 EUR DEL 27.02.2026 A (ITA) MACELLERIA BONI</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>11.62</v>
+        <v>26.03</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -3580,7 +3573,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Disposizione - RIF:219200234 BEN. UNIVERSITA' DEGLI STUDI DI BOLOGNA</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 9388 LIBRACCIO OVEST</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -3594,18 +3587,18 @@
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
-        <v>46080</v>
+        <v>46081</v>
       </c>
       <c r="B160" s="2" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:215528357 ORD. RICARICA POSTEPAY SOFIA</t>
-        </is>
-      </c>
-      <c r="E160" t="n">
-        <v>276.9</v>
+          <t>Pagam. POS - PAGAMENTO POS 161,23 EUR DEL 28.02.2026 A (ITA) MACELLERIA BONI</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>161.23</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
